--- a/Inst/extdata/factor_recode_in.xlsx
+++ b/Inst/extdata/factor_recode_in.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mrkmartongmailcom.sharepoint.com/sites/-/Shared Documents/General/Stats_R/R/Martysbloodsugar/Inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="280" documentId="11_D093DC72F6DA518C41C34F1CB7CD81C89631F60E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E207CE3-3F43-4860-AA57-287708C0D530}"/>
+  <xr:revisionPtr revIDLastSave="350" documentId="11_D093DC72F6DA518C41C34F1CB7CD81C89631F60E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA6A99B5-9670-458D-A70F-1E5448F52D4F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="237">
   <si>
     <t>time</t>
   </si>
@@ -452,9 +452,6 @@
     <t>hunger_high</t>
   </si>
   <si>
-    <t>almonds_100gr</t>
-  </si>
-  <si>
     <t>pasta</t>
   </si>
   <si>
@@ -500,9 +497,6 @@
     <t>confectionary_ischler</t>
   </si>
   <si>
-    <t>pomelo_half</t>
-  </si>
-  <si>
     <t>salami+cibatta</t>
   </si>
   <si>
@@ -557,9 +551,6 @@
     <t>paeanuts_50gr</t>
   </si>
   <si>
-    <t>citrus2</t>
-  </si>
-  <si>
     <t>eggsalad+buns+chocolate</t>
   </si>
   <si>
@@ -600,6 +591,159 @@
   </si>
   <si>
     <t>pasta+potato</t>
+  </si>
+  <si>
+    <t>ananas+blueberries 30min ago</t>
+  </si>
+  <si>
+    <t>rice+p.chops+brussel sprouts+bonbon</t>
+  </si>
+  <si>
+    <t>rice+beans+veal → rice+beans+veal+chocolate</t>
+  </si>
+  <si>
+    <t>peanuts150+nuts100+honey60 → peanuts150+nutz100+honey60-ate 80%</t>
+  </si>
+  <si>
+    <t>coffee w. oil</t>
+  </si>
+  <si>
+    <t>bubble tea</t>
+  </si>
+  <si>
+    <t>felt hypogl.</t>
+  </si>
+  <si>
+    <t>buns+veal+paté+sweets</t>
+  </si>
+  <si>
+    <t>almond150 → almond100</t>
+  </si>
+  <si>
+    <t>pulyka+krumpli+bejgli</t>
+  </si>
+  <si>
+    <t>turkey+bejgli</t>
+  </si>
+  <si>
+    <t>Snickers bar 50gr</t>
+  </si>
+  <si>
+    <t>hungry, medium</t>
+  </si>
+  <si>
+    <t>pogácsa</t>
+  </si>
+  <si>
+    <t>aspique → aspique+jam+bonbon+stuff</t>
+  </si>
+  <si>
+    <t>oat bran60+peas+turkey</t>
+  </si>
+  <si>
+    <t>hungry-medium → potato</t>
+  </si>
+  <si>
+    <t>cake decorating (not no caloric :)</t>
+  </si>
+  <si>
+    <t>white chocolate mud cake</t>
+  </si>
+  <si>
+    <t>coffee w milk100</t>
+  </si>
+  <si>
+    <t>hamburger 30dkg meat</t>
+  </si>
+  <si>
+    <t>cake kikelet (sugar free)</t>
+  </si>
+  <si>
+    <t>coffee w milk</t>
+  </si>
+  <si>
+    <t>running</t>
+  </si>
+  <si>
+    <t>futás vége</t>
+  </si>
+  <si>
+    <t>dinner (turkey bread pate kikelet cake)</t>
+  </si>
+  <si>
+    <t>grapefruit → ananas</t>
+  </si>
+  <si>
+    <t>bread+eggs+tuna → +grapefruit</t>
+  </si>
+  <si>
+    <t>ananas</t>
+  </si>
+  <si>
+    <t>eggs+bun</t>
+  </si>
+  <si>
+    <t>Nagy kakas burger → +bubble tea</t>
+  </si>
+  <si>
+    <t>headache</t>
+  </si>
+  <si>
+    <t>potatoes cake citrus</t>
+  </si>
+  <si>
+    <t>sushi</t>
+  </si>
+  <si>
+    <t>ananas + blueberries</t>
+  </si>
+  <si>
+    <t>rice+beans+veal+chocolate</t>
+  </si>
+  <si>
+    <t>peanuts120+nutz80+honey50</t>
+  </si>
+  <si>
+    <t>felt hypoglycemic</t>
+  </si>
+  <si>
+    <t>almond100</t>
+  </si>
+  <si>
+    <t>turkey + potatoes + confectionary</t>
+  </si>
+  <si>
+    <t>turkey + confectionary</t>
+  </si>
+  <si>
+    <t>scones</t>
+  </si>
+  <si>
+    <t>aspique+jam+bonbon+stuff</t>
+  </si>
+  <si>
+    <t>unspecified intake</t>
+  </si>
+  <si>
+    <t>coffee + milk 100</t>
+  </si>
+  <si>
+    <t>running ends</t>
+  </si>
+  <si>
+    <t>grapefruit + ananas</t>
+  </si>
+  <si>
+    <t>bread+eggs+tuna+grapefruit</t>
+  </si>
+  <si>
+    <t>Nagy kakas burger + bubble tea</t>
+  </si>
+  <si>
+    <t>citrus - grapefruit</t>
+  </si>
+  <si>
+    <t>citrus - pomelo</t>
   </si>
 </sst>
 </file>
@@ -956,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" style="2" customWidth="1"/>
@@ -1533,7 +1677,7 @@
         <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="D41" t="s">
         <v>111</v>
@@ -1547,7 +1691,7 @@
         <v>42</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D42" t="s">
         <v>111</v>
@@ -1561,7 +1705,7 @@
         <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D43" t="s">
         <v>111</v>
@@ -1589,7 +1733,7 @@
         <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D45" t="s">
         <v>111</v>
@@ -1617,7 +1761,7 @@
         <v>47</v>
       </c>
       <c r="C47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D47" t="s">
         <v>111</v>
@@ -1631,7 +1775,7 @@
         <v>48</v>
       </c>
       <c r="C48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D48" t="s">
         <v>111</v>
@@ -1645,7 +1789,7 @@
         <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D49" t="s">
         <v>111</v>
@@ -1659,7 +1803,7 @@
         <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D50" t="s">
         <v>111</v>
@@ -1673,7 +1817,7 @@
         <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D51" t="s">
         <v>111</v>
@@ -1687,7 +1831,7 @@
         <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D52" t="s">
         <v>111</v>
@@ -1701,7 +1845,7 @@
         <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D53" t="s">
         <v>111</v>
@@ -1715,7 +1859,7 @@
         <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D54" t="s">
         <v>114</v>
@@ -1729,7 +1873,7 @@
         <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D55" t="s">
         <v>111</v>
@@ -1743,7 +1887,7 @@
         <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D56" t="s">
         <v>111</v>
@@ -1757,7 +1901,7 @@
         <v>57</v>
       </c>
       <c r="C57" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="D57" t="s">
         <v>111</v>
@@ -1771,7 +1915,7 @@
         <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D58" t="s">
         <v>111</v>
@@ -1785,7 +1929,7 @@
         <v>51</v>
       </c>
       <c r="C59" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D59" t="s">
         <v>111</v>
@@ -1799,7 +1943,7 @@
         <v>59</v>
       </c>
       <c r="C60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D60" t="s">
         <v>111</v>
@@ -1841,7 +1985,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="D63" t="s">
         <v>111</v>
@@ -1855,7 +1999,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D64" t="s">
         <v>111</v>
@@ -1869,7 +2013,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D65" t="s">
         <v>111</v>
@@ -1897,7 +2041,7 @@
         <v>51</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D67" t="s">
         <v>111</v>
@@ -1911,7 +2055,7 @@
         <v>64</v>
       </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D68" t="s">
         <v>114</v>
@@ -1925,7 +2069,7 @@
         <v>57</v>
       </c>
       <c r="C69" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="D69" t="s">
         <v>111</v>
@@ -1939,7 +2083,7 @@
         <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D70" t="s">
         <v>111</v>
@@ -1953,7 +2097,7 @@
         <v>66</v>
       </c>
       <c r="C71" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D71" t="s">
         <v>111</v>
@@ -1967,7 +2111,7 @@
         <v>67</v>
       </c>
       <c r="C72" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D72" t="s">
         <v>114</v>
@@ -1981,7 +2125,7 @@
         <v>68</v>
       </c>
       <c r="C73" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D73" t="s">
         <v>111</v>
@@ -1995,7 +2139,7 @@
         <v>51</v>
       </c>
       <c r="C74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D74" t="s">
         <v>111</v>
@@ -2009,7 +2153,7 @@
         <v>69</v>
       </c>
       <c r="C75" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D75" t="s">
         <v>111</v>
@@ -2023,7 +2167,7 @@
         <v>70</v>
       </c>
       <c r="C76" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D76" t="s">
         <v>111</v>
@@ -2037,7 +2181,7 @@
         <v>71</v>
       </c>
       <c r="C77" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D77" t="s">
         <v>111</v>
@@ -2051,7 +2195,7 @@
         <v>72</v>
       </c>
       <c r="C78" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D78" t="s">
         <v>111</v>
@@ -2065,7 +2209,7 @@
         <v>73</v>
       </c>
       <c r="C79" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D79" t="s">
         <v>111</v>
@@ -2079,7 +2223,7 @@
         <v>74</v>
       </c>
       <c r="C80" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="D80" t="s">
         <v>111</v>
@@ -2093,7 +2237,7 @@
         <v>75</v>
       </c>
       <c r="C81" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
         <v>111</v>
@@ -2121,7 +2265,7 @@
         <v>77</v>
       </c>
       <c r="C83" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D83" t="s">
         <v>111</v>
@@ -2135,7 +2279,7 @@
         <v>78</v>
       </c>
       <c r="C84" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D84" t="s">
         <v>111</v>
@@ -2149,7 +2293,7 @@
         <v>79</v>
       </c>
       <c r="C85" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="D85" t="s">
         <v>111</v>
@@ -2163,7 +2307,7 @@
         <v>57</v>
       </c>
       <c r="C86" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="D86" t="s">
         <v>111</v>
@@ -2177,7 +2321,7 @@
         <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D87" t="s">
         <v>111</v>
@@ -2191,7 +2335,7 @@
         <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D88" t="s">
         <v>111</v>
@@ -2205,7 +2349,7 @@
         <v>82</v>
       </c>
       <c r="C89" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D89" t="s">
         <v>111</v>
@@ -2219,7 +2363,7 @@
         <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D90" t="s">
         <v>111</v>
@@ -2233,7 +2377,7 @@
         <v>83</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D91" t="s">
         <v>114</v>
@@ -2247,7 +2391,7 @@
         <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D92" t="s">
         <v>111</v>
@@ -2261,7 +2405,7 @@
         <v>85</v>
       </c>
       <c r="C93" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D93" t="s">
         <v>111</v>
@@ -2275,7 +2419,7 @@
         <v>86</v>
       </c>
       <c r="C94" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D94" t="s">
         <v>111</v>
@@ -2303,7 +2447,7 @@
         <v>87</v>
       </c>
       <c r="C96" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="D96" t="s">
         <v>111</v>
@@ -2317,7 +2461,7 @@
         <v>88</v>
       </c>
       <c r="C97" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D97" t="s">
         <v>111</v>
@@ -2345,7 +2489,7 @@
         <v>90</v>
       </c>
       <c r="C99" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D99" t="s">
         <v>111</v>
@@ -2359,7 +2503,7 @@
         <v>91</v>
       </c>
       <c r="C100" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D100" t="s">
         <v>111</v>
@@ -2373,7 +2517,7 @@
         <v>92</v>
       </c>
       <c r="C101" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D101" t="s">
         <v>114</v>
@@ -2387,7 +2531,7 @@
         <v>93</v>
       </c>
       <c r="C102" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D102" t="s">
         <v>114</v>
@@ -2415,7 +2559,7 @@
         <v>95</v>
       </c>
       <c r="C104" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D104" t="s">
         <v>111</v>
@@ -2443,7 +2587,7 @@
         <v>97</v>
       </c>
       <c r="C106" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D106" t="s">
         <v>111</v>
@@ -2457,7 +2601,7 @@
         <v>98</v>
       </c>
       <c r="C107" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D107" t="s">
         <v>111</v>
@@ -2471,7 +2615,7 @@
         <v>99</v>
       </c>
       <c r="C108" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D108" t="s">
         <v>111</v>
@@ -2485,7 +2629,7 @@
         <v>100</v>
       </c>
       <c r="C109" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D109" t="s">
         <v>111</v>
@@ -2499,7 +2643,7 @@
         <v>82</v>
       </c>
       <c r="C110" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D110" t="s">
         <v>111</v>
@@ -2513,7 +2657,7 @@
         <v>101</v>
       </c>
       <c r="C111" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D111" t="s">
         <v>111</v>
@@ -2527,7 +2671,7 @@
         <v>102</v>
       </c>
       <c r="C112" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D112" t="s">
         <v>111</v>
@@ -2541,7 +2685,7 @@
         <v>103</v>
       </c>
       <c r="C113" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D113" t="s">
         <v>111</v>
@@ -2555,7 +2699,7 @@
         <v>104</v>
       </c>
       <c r="C114" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D114" t="s">
         <v>111</v>
@@ -2597,7 +2741,7 @@
         <v>106</v>
       </c>
       <c r="C117" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D117" t="s">
         <v>111</v>
@@ -2615,6 +2759,594 @@
       </c>
       <c r="D118" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>45281.737007673612</v>
+      </c>
+      <c r="B119" t="s">
+        <v>2</v>
+      </c>
+      <c r="C119" t="s">
+        <v>109</v>
+      </c>
+      <c r="D119" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>45281.725659722222</v>
+      </c>
+      <c r="B120" t="s">
+        <v>186</v>
+      </c>
+      <c r="C120" t="s">
+        <v>220</v>
+      </c>
+      <c r="D120" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>45281.850544525463</v>
+      </c>
+      <c r="B121" t="s">
+        <v>187</v>
+      </c>
+      <c r="C121" t="s">
+        <v>187</v>
+      </c>
+      <c r="D121" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>45282.321540393517</v>
+      </c>
+      <c r="B122" t="s">
+        <v>187</v>
+      </c>
+      <c r="C122" t="s">
+        <v>187</v>
+      </c>
+      <c r="D122" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>45282.589807951394</v>
+      </c>
+      <c r="B123" t="s">
+        <v>188</v>
+      </c>
+      <c r="C123" t="s">
+        <v>221</v>
+      </c>
+      <c r="D123" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>45282.782803414353</v>
+      </c>
+      <c r="B124" t="s">
+        <v>189</v>
+      </c>
+      <c r="C124" t="s">
+        <v>222</v>
+      </c>
+      <c r="D124" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>45283.368358738429</v>
+      </c>
+      <c r="B125" t="s">
+        <v>190</v>
+      </c>
+      <c r="C125" t="s">
+        <v>122</v>
+      </c>
+      <c r="D125" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>45283.473503182868</v>
+      </c>
+      <c r="B126" t="s">
+        <v>191</v>
+      </c>
+      <c r="C126" t="s">
+        <v>191</v>
+      </c>
+      <c r="D126" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <v>45283.593633460652</v>
+      </c>
+      <c r="B127" t="s">
+        <v>192</v>
+      </c>
+      <c r="C127" t="s">
+        <v>223</v>
+      </c>
+      <c r="D127" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
+        <v>45283.609496157413</v>
+      </c>
+      <c r="B128" t="s">
+        <v>193</v>
+      </c>
+      <c r="C128" t="s">
+        <v>193</v>
+      </c>
+      <c r="D128" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>45284.403387847233</v>
+      </c>
+      <c r="B129" t="s">
+        <v>194</v>
+      </c>
+      <c r="C129" t="s">
+        <v>224</v>
+      </c>
+      <c r="D129" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
+        <v>45284.534891828713</v>
+      </c>
+      <c r="B130" t="s">
+        <v>195</v>
+      </c>
+      <c r="C130" t="s">
+        <v>225</v>
+      </c>
+      <c r="D130" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
+        <v>45284.848829328708</v>
+      </c>
+      <c r="B131" t="s">
+        <v>196</v>
+      </c>
+      <c r="C131" t="s">
+        <v>226</v>
+      </c>
+      <c r="D131" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>45285.44408671296</v>
+      </c>
+      <c r="B132" t="s">
+        <v>197</v>
+      </c>
+      <c r="C132" t="s">
+        <v>197</v>
+      </c>
+      <c r="D132" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>45285.513170833343</v>
+      </c>
+      <c r="B133" t="s">
+        <v>198</v>
+      </c>
+      <c r="C133" t="s">
+        <v>198</v>
+      </c>
+      <c r="D133" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>45285.552977650463</v>
+      </c>
+      <c r="B134" t="s">
+        <v>199</v>
+      </c>
+      <c r="C134" t="s">
+        <v>227</v>
+      </c>
+      <c r="D134" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="2">
+        <v>45285.756346168993</v>
+      </c>
+      <c r="B135" t="s">
+        <v>200</v>
+      </c>
+      <c r="C135" t="s">
+        <v>228</v>
+      </c>
+      <c r="D135" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
+        <v>45286.384691481479</v>
+      </c>
+      <c r="B136" t="s">
+        <v>201</v>
+      </c>
+      <c r="C136" t="s">
+        <v>201</v>
+      </c>
+      <c r="D136" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>45286.537970023142</v>
+      </c>
+      <c r="B137" t="s">
+        <v>202</v>
+      </c>
+      <c r="C137" t="s">
+        <v>182</v>
+      </c>
+      <c r="D137" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
+        <v>45286.54368923611</v>
+      </c>
+      <c r="B138" t="s">
+        <v>203</v>
+      </c>
+      <c r="C138" t="s">
+        <v>229</v>
+      </c>
+      <c r="D138" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <v>45286.670216701386</v>
+      </c>
+      <c r="B139" t="s">
+        <v>204</v>
+      </c>
+      <c r="C139" t="s">
+        <v>204</v>
+      </c>
+      <c r="D139" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <v>45287.368560891213</v>
+      </c>
+      <c r="B140" t="s">
+        <v>204</v>
+      </c>
+      <c r="C140" t="s">
+        <v>204</v>
+      </c>
+      <c r="D140" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="2">
+        <v>45287.559550763886</v>
+      </c>
+      <c r="B141" t="s">
+        <v>205</v>
+      </c>
+      <c r="C141" t="s">
+        <v>230</v>
+      </c>
+      <c r="D141" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <v>45287.574621689811</v>
+      </c>
+      <c r="B142" t="s">
+        <v>206</v>
+      </c>
+      <c r="C142" t="s">
+        <v>206</v>
+      </c>
+      <c r="D142" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="2">
+        <v>45288.353241863428</v>
+      </c>
+      <c r="B143" t="s">
+        <v>207</v>
+      </c>
+      <c r="C143" t="s">
+        <v>207</v>
+      </c>
+      <c r="D143" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>45288.576182141202</v>
+      </c>
+      <c r="B144" t="s">
+        <v>208</v>
+      </c>
+      <c r="C144" t="s">
+        <v>230</v>
+      </c>
+      <c r="D144" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>45288.595600601853</v>
+      </c>
+      <c r="B145" t="s">
+        <v>209</v>
+      </c>
+      <c r="C145" t="s">
+        <v>209</v>
+      </c>
+      <c r="D145" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>45288.630962407413</v>
+      </c>
+      <c r="B146" t="s">
+        <v>210</v>
+      </c>
+      <c r="C146" t="s">
+        <v>231</v>
+      </c>
+      <c r="D146" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="2">
+        <v>45288.67249704861</v>
+      </c>
+      <c r="B147" t="s">
+        <v>211</v>
+      </c>
+      <c r="C147" t="s">
+        <v>211</v>
+      </c>
+      <c r="D147" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
+        <v>45288.867047187501</v>
+      </c>
+      <c r="B148" t="s">
+        <v>212</v>
+      </c>
+      <c r="C148" t="s">
+        <v>232</v>
+      </c>
+      <c r="D148" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>45289.227199803237</v>
+      </c>
+      <c r="B149" t="s">
+        <v>204</v>
+      </c>
+      <c r="C149" t="s">
+        <v>204</v>
+      </c>
+      <c r="D149" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>45289.534808402779</v>
+      </c>
+      <c r="B150" t="s">
+        <v>204</v>
+      </c>
+      <c r="C150" t="s">
+        <v>204</v>
+      </c>
+      <c r="D150" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <v>45289.714302094908</v>
+      </c>
+      <c r="B151" t="s">
+        <v>213</v>
+      </c>
+      <c r="C151" t="s">
+        <v>233</v>
+      </c>
+      <c r="D151" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>45289.833333333336</v>
+      </c>
+      <c r="B152" t="s">
+        <v>214</v>
+      </c>
+      <c r="C152" t="s">
+        <v>214</v>
+      </c>
+      <c r="D152" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>45290.340660173613</v>
+      </c>
+      <c r="B153" t="s">
+        <v>215</v>
+      </c>
+      <c r="C153" t="s">
+        <v>215</v>
+      </c>
+      <c r="D153" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>45290.408333333333</v>
+      </c>
+      <c r="B154" t="s">
+        <v>209</v>
+      </c>
+      <c r="C154" t="s">
+        <v>209</v>
+      </c>
+      <c r="D154" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <v>45290.525819490736</v>
+      </c>
+      <c r="B155" t="s">
+        <v>216</v>
+      </c>
+      <c r="C155" t="s">
+        <v>234</v>
+      </c>
+      <c r="D155" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>45290.618235937502</v>
+      </c>
+      <c r="B156" t="s">
+        <v>217</v>
+      </c>
+      <c r="C156" t="s">
+        <v>217</v>
+      </c>
+      <c r="D156" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>45290.802963935188</v>
+      </c>
+      <c r="B157" t="s">
+        <v>218</v>
+      </c>
+      <c r="C157" t="s">
+        <v>218</v>
+      </c>
+      <c r="D157" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>45291.326597500003</v>
+      </c>
+      <c r="B158" t="s">
+        <v>117</v>
+      </c>
+      <c r="C158" t="s">
+        <v>117</v>
+      </c>
+      <c r="D158" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <v>45291.466283240741</v>
+      </c>
+      <c r="B159" t="s">
+        <v>87</v>
+      </c>
+      <c r="C159" t="s">
+        <v>87</v>
+      </c>
+      <c r="D159" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>45291.517906400462</v>
+      </c>
+      <c r="B160" t="s">
+        <v>219</v>
+      </c>
+      <c r="C160" t="s">
+        <v>219</v>
+      </c>
+      <c r="D160" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2623,6 +3355,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F0ADBC3A86B10A4085B52F181C274AA0" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8197e89490dc663f80df425c475dfb63">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3073c576-dbcc-4dca-a8e5-ccf7a0688d93" xmlns:ns3="a95d4ba5-ac50-4ccb-8f38-68d250b34105" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="57d494f76f6743b951aebebbdbb44cb6" ns2:_="" ns3:_="">
     <xsd:import namespace="3073c576-dbcc-4dca-a8e5-ccf7a0688d93"/>
@@ -2837,16 +3578,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{345060A5-AE88-4A9B-A948-EA83BD25AEA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB7476A-D723-4489-BA50-730EE7EDBB98}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2863,12 +3603,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{345060A5-AE88-4A9B-A948-EA83BD25AEA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>